--- a/Not_Eligible.xlsx
+++ b/Not_Eligible.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I29"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -502,16 +502,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="str">
-        <v xml:space="preserve">ABHAY C GEORGE </v>
-      </c>
-      <c r="C4">
-        <v>99999</v>
+        <v>ANOOP L R</v>
+      </c>
+      <c r="C4" t="str">
+        <v>0</v>
       </c>
       <c r="D4" t="str">
-        <v>68%</v>
+        <v>87.78%</v>
       </c>
       <c r="E4" t="str">
-        <v>OBC Christian</v>
+        <v>Ezhava</v>
       </c>
       <c r="F4" t="str">
         <v>LET Exam Not Attended</v>
@@ -531,16 +531,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="str">
-        <v>ANOOP L R</v>
-      </c>
-      <c r="C5">
-        <v>99999</v>
+        <v xml:space="preserve">ABHAY C GEORGE </v>
+      </c>
+      <c r="C5" t="str">
+        <v>0</v>
       </c>
       <c r="D5" t="str">
-        <v>87.78%</v>
+        <v>68%</v>
       </c>
       <c r="E5" t="str">
-        <v>Ezhava</v>
+        <v>OBC Christian</v>
       </c>
       <c r="F5" t="str">
         <v>LET Exam Not Attended</v>
@@ -560,16 +560,16 @@
         <v>3</v>
       </c>
       <c r="B6" t="str">
-        <v>Sreelal .C.S</v>
-      </c>
-      <c r="C6">
-        <v>99999</v>
+        <v>Abu thahir S</v>
+      </c>
+      <c r="C6" t="str">
+        <v>0</v>
       </c>
       <c r="D6" t="str">
-        <v>79.04%</v>
+        <v>75.6%</v>
       </c>
       <c r="E6" t="str">
-        <v>Ezhava</v>
+        <v>Muslim</v>
       </c>
       <c r="F6" t="str">
         <v>LET Exam Not Attended</v>
@@ -578,10 +578,10 @@
         <v>Diploma</v>
       </c>
       <c r="H6" t="str">
-        <v>11 km</v>
+        <v>10 km</v>
       </c>
       <c r="I6" t="str">
-        <v>23 yrs</v>
+        <v>4 yrs</v>
       </c>
     </row>
     <row r="7">
@@ -589,28 +589,28 @@
         <v>4</v>
       </c>
       <c r="B7" t="str">
-        <v>Vaishakhi M</v>
-      </c>
-      <c r="C7">
-        <v>99999</v>
+        <v>SUNIL KUMAR B</v>
+      </c>
+      <c r="C7" t="str">
+        <v>0</v>
       </c>
       <c r="D7" t="str">
-        <v>81%</v>
+        <v>68.31%</v>
       </c>
       <c r="E7" t="str">
-        <v>Other Backward Hindu</v>
+        <v>SC</v>
       </c>
       <c r="F7" t="str">
         <v>LET Exam Not Attended</v>
       </c>
       <c r="G7" t="str">
-        <v>BTech</v>
+        <v>Diploma</v>
       </c>
       <c r="H7" t="str">
-        <v>8 km</v>
+        <v>0 km</v>
       </c>
       <c r="I7" t="str">
-        <v>null</v>
+        <v>26 yrs</v>
       </c>
     </row>
     <row r="8">
@@ -618,16 +618,16 @@
         <v>5</v>
       </c>
       <c r="B8" t="str">
-        <v>SUNIL KUMAR B</v>
-      </c>
-      <c r="C8">
-        <v>99999</v>
+        <v>Yogesh Kumar Gupta</v>
+      </c>
+      <c r="C8" t="str">
+        <v>0</v>
       </c>
       <c r="D8" t="str">
-        <v>68.31%</v>
+        <v>79.44%</v>
       </c>
       <c r="E8" t="str">
-        <v>SC</v>
+        <v>Central govt. employee</v>
       </c>
       <c r="F8" t="str">
         <v>LET Exam Not Attended</v>
@@ -636,10 +636,10 @@
         <v>Diploma</v>
       </c>
       <c r="H8" t="str">
-        <v>0 km</v>
+        <v>5 km</v>
       </c>
       <c r="I8" t="str">
-        <v>26 yrs</v>
+        <v>2.5 yrs</v>
       </c>
     </row>
     <row r="9">
@@ -649,8 +649,8 @@
       <c r="B9" t="str">
         <v>Manju K</v>
       </c>
-      <c r="C9">
-        <v>99999</v>
+      <c r="C9" t="str">
+        <v>0</v>
       </c>
       <c r="D9" t="str">
         <v>67.6%</v>
@@ -676,16 +676,16 @@
         <v>7</v>
       </c>
       <c r="B10" t="str">
-        <v>Abu thahir S</v>
-      </c>
-      <c r="C10">
-        <v>99999</v>
+        <v>Navaneeth B Vijayan</v>
+      </c>
+      <c r="C10" t="str">
+        <v>0</v>
       </c>
       <c r="D10" t="str">
-        <v>75.6%</v>
+        <v>93.3%</v>
       </c>
       <c r="E10" t="str">
-        <v>Muslim</v>
+        <v>Ezhava</v>
       </c>
       <c r="F10" t="str">
         <v>LET Exam Not Attended</v>
@@ -694,10 +694,10 @@
         <v>Diploma</v>
       </c>
       <c r="H10" t="str">
-        <v>10 km</v>
+        <v>6.5 km</v>
       </c>
       <c r="I10" t="str">
-        <v>4 yrs</v>
+        <v>1 yrs</v>
       </c>
     </row>
     <row r="11">
@@ -705,16 +705,16 @@
         <v>8</v>
       </c>
       <c r="B11" t="str">
-        <v>Sarath R S</v>
-      </c>
-      <c r="C11">
-        <v>99999</v>
+        <v>Shilpa S</v>
+      </c>
+      <c r="C11" t="str">
+        <v>0</v>
       </c>
       <c r="D11" t="str">
-        <v>66.4%</v>
+        <v>75.4%</v>
       </c>
       <c r="E11" t="str">
-        <v>General</v>
+        <v>SC</v>
       </c>
       <c r="F11" t="str">
         <v>LET Exam Not Attended</v>
@@ -723,10 +723,10 @@
         <v>Diploma</v>
       </c>
       <c r="H11" t="str">
-        <v>5.2 km</v>
+        <v>5.5 km</v>
       </c>
       <c r="I11" t="str">
-        <v>5 yrs</v>
+        <v>1 yrs</v>
       </c>
     </row>
     <row r="12">
@@ -734,16 +734,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="str">
-        <v>Yogesh Kumar Gupta</v>
-      </c>
-      <c r="C12">
-        <v>99999</v>
+        <v>Sarath R S</v>
+      </c>
+      <c r="C12" t="str">
+        <v>0</v>
       </c>
       <c r="D12" t="str">
-        <v>79.44%</v>
+        <v>66.4%</v>
       </c>
       <c r="E12" t="str">
-        <v>Central govt. employee</v>
+        <v>General</v>
       </c>
       <c r="F12" t="str">
         <v>LET Exam Not Attended</v>
@@ -752,10 +752,10 @@
         <v>Diploma</v>
       </c>
       <c r="H12" t="str">
-        <v>5 km</v>
+        <v>5.2 km</v>
       </c>
       <c r="I12" t="str">
-        <v>2.5 yrs</v>
+        <v>5 yrs</v>
       </c>
     </row>
     <row r="13">
@@ -763,13 +763,13 @@
         <v>10</v>
       </c>
       <c r="B13" t="str">
-        <v>Navaneeth B Vijayan</v>
-      </c>
-      <c r="C13">
-        <v>99999</v>
+        <v>Athul Muraleedharan</v>
+      </c>
+      <c r="C13" t="str">
+        <v>0</v>
       </c>
       <c r="D13" t="str">
-        <v>93.3%</v>
+        <v>80.37%</v>
       </c>
       <c r="E13" t="str">
         <v>Ezhava</v>
@@ -784,7 +784,7 @@
         <v>6.5 km</v>
       </c>
       <c r="I13" t="str">
-        <v>1 yrs</v>
+        <v>3.5 yrs</v>
       </c>
     </row>
     <row r="14">
@@ -792,13 +792,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="str">
-        <v>Athul Muraleedharan</v>
-      </c>
-      <c r="C14">
-        <v>99999</v>
+        <v>Sreelal .C.S</v>
+      </c>
+      <c r="C14" t="str">
+        <v>0</v>
       </c>
       <c r="D14" t="str">
-        <v>80.37%</v>
+        <v>79.04%</v>
       </c>
       <c r="E14" t="str">
         <v>Ezhava</v>
@@ -810,10 +810,10 @@
         <v>Diploma</v>
       </c>
       <c r="H14" t="str">
-        <v>6.5 km</v>
+        <v>11 km</v>
       </c>
       <c r="I14" t="str">
-        <v>3.5 yrs</v>
+        <v>23 yrs</v>
       </c>
     </row>
     <row r="15">
@@ -821,28 +821,434 @@
         <v>12</v>
       </c>
       <c r="B15" t="str">
-        <v>Shilpa S</v>
-      </c>
-      <c r="C15">
-        <v>99999</v>
+        <v>Vaishakhi M</v>
+      </c>
+      <c r="C15" t="str">
+        <v>0</v>
       </c>
       <c r="D15" t="str">
-        <v>75.4%</v>
+        <v>81%</v>
       </c>
       <c r="E15" t="str">
+        <v>Other Backward Hindu</v>
+      </c>
+      <c r="F15" t="str">
+        <v>LET Exam Not Attended</v>
+      </c>
+      <c r="G15" t="str">
+        <v>BTech</v>
+      </c>
+      <c r="H15" t="str">
+        <v>8 km</v>
+      </c>
+      <c r="I15" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="str">
+        <v xml:space="preserve">Sourav sunil </v>
+      </c>
+      <c r="C16" t="str">
+        <v>0</v>
+      </c>
+      <c r="D16" t="str">
+        <v>71.4%</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Ezhava</v>
+      </c>
+      <c r="F16" t="str">
+        <v>LET Exam Not Attended</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Diploma</v>
+      </c>
+      <c r="H16" t="str">
+        <v>65 km</v>
+      </c>
+      <c r="I16" t="str">
+        <v>1 yrs</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="str">
+        <v>ANUROOP A R</v>
+      </c>
+      <c r="C17" t="str">
+        <v>0</v>
+      </c>
+      <c r="D17" t="str">
+        <v>74.76%</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Ezhava</v>
+      </c>
+      <c r="F17" t="str">
+        <v>LET Exam Not Attended</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Diploma</v>
+      </c>
+      <c r="H17" t="str">
+        <v>6 km</v>
+      </c>
+      <c r="I17" t="str">
+        <v>3 yrs</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Jismon Joshy</v>
+      </c>
+      <c r="C18" t="str">
+        <v>0</v>
+      </c>
+      <c r="D18" t="str">
+        <v>74.47%</v>
+      </c>
+      <c r="E18" t="str">
+        <v>EWS</v>
+      </c>
+      <c r="F18" t="str">
+        <v>LET Exam Not Attended</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Diploma</v>
+      </c>
+      <c r="H18" t="str">
+        <v>70 km</v>
+      </c>
+      <c r="I18" t="str">
+        <v>266 yrs</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Karthik P R</v>
+      </c>
+      <c r="C19" t="str">
+        <v>0</v>
+      </c>
+      <c r="D19" t="str">
+        <v>72.2%</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Other Backward Hindu</v>
+      </c>
+      <c r="F19" t="str">
+        <v>LET Exam Not Attended</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Diploma</v>
+      </c>
+      <c r="H19" t="str">
+        <v>7 km</v>
+      </c>
+      <c r="I19" t="str">
+        <v>1.5 yrs</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" t="str">
+        <v>NIZAMUDEEN B</v>
+      </c>
+      <c r="C20" t="str">
+        <v>0</v>
+      </c>
+      <c r="D20" t="str">
+        <v>71.714%</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Central govt. employee</v>
+      </c>
+      <c r="F20" t="str">
+        <v>LET Exam Not Attended</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Diploma</v>
+      </c>
+      <c r="H20" t="str">
+        <v>7.5 km</v>
+      </c>
+      <c r="I20" t="str">
+        <v>18 yrs</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Melwin Joshy</v>
+      </c>
+      <c r="C21" t="str">
+        <v>0</v>
+      </c>
+      <c r="D21" t="str">
+        <v>89.3%</v>
+      </c>
+      <c r="E21" t="str">
+        <v>General</v>
+      </c>
+      <c r="F21" t="str">
+        <v>LET Exam Not Attended</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Diploma</v>
+      </c>
+      <c r="H21" t="str">
+        <v>6.9 km</v>
+      </c>
+      <c r="I21" t="str">
+        <v>1 yrs</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Muhammad Rashid U H</v>
+      </c>
+      <c r="C22" t="str">
+        <v>0</v>
+      </c>
+      <c r="D22" t="str">
+        <v>89.3%</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Muslim</v>
+      </c>
+      <c r="F22" t="str">
+        <v>LET Exam Not Attended</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Diploma</v>
+      </c>
+      <c r="H22" t="str">
+        <v>6.6 km</v>
+      </c>
+      <c r="I22" t="str">
+        <v>0.1 yrs</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" t="str">
+        <v>GOUTHAM T G</v>
+      </c>
+      <c r="C23" t="str">
+        <v>0</v>
+      </c>
+      <c r="D23" t="str">
+        <v>72.675%</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Kudumbi</v>
+      </c>
+      <c r="F23" t="str">
+        <v>LET Exam Not Attended</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Diploma</v>
+      </c>
+      <c r="H23" t="str">
+        <v>6.6 km</v>
+      </c>
+      <c r="I23" t="str">
+        <v>1 yrs</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="str">
+        <v>NIYASUDHEEN MOITHU</v>
+      </c>
+      <c r="C24" t="str">
+        <v>0</v>
+      </c>
+      <c r="D24" t="str">
+        <v>95.9%</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Muslim</v>
+      </c>
+      <c r="F24" t="str">
+        <v>LET Exam Not Attended</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Diploma</v>
+      </c>
+      <c r="H24" t="str">
+        <v>7.2 km</v>
+      </c>
+      <c r="I24" t="str">
+        <v>1 yrs</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="str">
+        <v>N M Ohmnath Shenoy</v>
+      </c>
+      <c r="C25" t="str">
+        <v>0</v>
+      </c>
+      <c r="D25" t="str">
+        <v>61.75%</v>
+      </c>
+      <c r="E25" t="str">
+        <v>General</v>
+      </c>
+      <c r="F25" t="str">
+        <v>LET Exam Not Attended</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Diploma</v>
+      </c>
+      <c r="H25" t="str">
+        <v>10 km</v>
+      </c>
+      <c r="I25" t="str">
+        <v>1.5 yrs</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Rakshith B</v>
+      </c>
+      <c r="C26" t="str">
+        <v>0</v>
+      </c>
+      <c r="D26" t="str">
+        <v>78.185%</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Ezhava</v>
+      </c>
+      <c r="F26" t="str">
+        <v>LET Exam Not Attended</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Diploma</v>
+      </c>
+      <c r="H26" t="str">
+        <v>6.6 km</v>
+      </c>
+      <c r="I26" t="str">
+        <v>0.1 yrs</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" t="str">
+        <v>AKSHAY S NAIR</v>
+      </c>
+      <c r="C27" t="str">
+        <v>0</v>
+      </c>
+      <c r="D27" t="str">
+        <v>47.2%</v>
+      </c>
+      <c r="E27" t="str">
+        <v>General</v>
+      </c>
+      <c r="F27" t="str">
+        <v>LET Exam Not Attended</v>
+      </c>
+      <c r="G27" t="str">
+        <v>BE</v>
+      </c>
+      <c r="H27" t="str">
+        <v>0 km</v>
+      </c>
+      <c r="I27" t="str">
+        <v>1 yrs</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" t="str">
+        <v>SHIBU L</v>
+      </c>
+      <c r="C28" t="str">
+        <v>0</v>
+      </c>
+      <c r="D28" t="str">
+        <v>84.17%</v>
+      </c>
+      <c r="E28" t="str">
         <v>SC</v>
       </c>
-      <c r="F15" t="str">
-        <v>LET Exam Not Attended</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Diploma</v>
-      </c>
-      <c r="H15" t="str">
-        <v>5.5 km</v>
-      </c>
-      <c r="I15" t="str">
+      <c r="F28" t="str">
+        <v>LET Exam Not Attended</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Diploma</v>
+      </c>
+      <c r="H28" t="str">
+        <v>12 km</v>
+      </c>
+      <c r="I28" t="str">
         <v>1 yrs</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Vibhin T</v>
+      </c>
+      <c r="C29" t="str">
+        <v>0</v>
+      </c>
+      <c r="D29" t="str">
+        <v>76%</v>
+      </c>
+      <c r="E29" t="str">
+        <v>OBC Christian</v>
+      </c>
+      <c r="F29" t="str">
+        <v>LET Exam Not Attended</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Diploma</v>
+      </c>
+      <c r="H29" t="str">
+        <v>5 km</v>
+      </c>
+      <c r="I29" t="str">
+        <v>20 yrs</v>
       </c>
     </row>
   </sheetData>
@@ -851,7 +1257,7 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I29"/>
   </ignoredErrors>
 </worksheet>
 </file>